--- a/metadata/plate_metadata/20260324_cep290_30hpf_plate01_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_30hpf_plate01_well_metadata.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1412,6 +1412,18 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="H22" s="10" t="n"/>
     </row>
